--- a/artfynd/A 55952-2024 artfynd.xlsx
+++ b/artfynd/A 55952-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AZ62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116247</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -932,6 +942,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1062,6 +1077,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116249</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1192,6 +1212,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89116251</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1322,6 +1347,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850496</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1452,6 +1482,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850497</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1582,6 +1617,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850499</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1712,6 +1752,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850642</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1842,6 +1887,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850643</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1972,6 +2022,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850644</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2102,6 +2157,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850645</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2232,6 +2292,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850646</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2362,6 +2427,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850647</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2492,6 +2562,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850648</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2622,6 +2697,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850649</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2752,6 +2832,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2882,6 +2967,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850651</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3012,6 +3102,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850652</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3142,6 +3237,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850653</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3272,6 +3372,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850654</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3402,6 +3507,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850658</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3532,6 +3642,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850661</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3662,6 +3777,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850662</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3792,6 +3912,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850663</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3922,6 +4047,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850664</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4052,6 +4182,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850666</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4182,6 +4317,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850667</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4312,6 +4452,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850669</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4442,6 +4587,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850670</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4572,6 +4722,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96850685</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4706,6 +4861,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040743</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4840,6 +5000,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040745</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4974,6 +5139,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040747</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5108,6 +5278,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040749</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5242,6 +5417,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040800</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5376,6 +5556,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040801</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5510,6 +5695,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040893</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5644,6 +5834,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040894</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5778,6 +5973,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040895</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5912,6 +6112,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040896</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6046,6 +6251,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040897</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6180,6 +6390,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105040898</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6314,6 +6529,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041038</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6448,6 +6668,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041039</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6582,6 +6807,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041206</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6716,6 +6946,11 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041208</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6841,6 +7076,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675761</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6966,6 +7206,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111675763</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7105,6 +7350,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062580</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7244,6 +7494,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062581</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7383,6 +7638,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062582</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7522,6 +7782,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062583</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7661,6 +7926,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062584</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7800,6 +8070,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062585</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7939,6 +8214,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062587</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8078,6 +8358,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062589</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8217,6 +8502,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062590</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8356,6 +8646,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062591</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8495,6 +8790,11 @@
           <t xml:space="preserve">Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121062592</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8634,6 +8934,11 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635622</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8773,8 +9078,76 @@
           <t xml:space="preserve">Biogeografisk uppföljning av fjärilar, Asknätfjäril i AB län </t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129635623</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>